--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4120"/>
+  <dimension ref="A1:B4132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33396,6 +33396,102 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4121">
+      <c r="A4121" s="2" t="n">
+        <v>46040</v>
+      </c>
+      <c r="B4121" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4122">
+      <c r="A4122" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B4122" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4123">
+      <c r="A4123" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B4123" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4124">
+      <c r="A4124" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B4124" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4125">
+      <c r="A4125" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B4125" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4126">
+      <c r="A4126" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B4126" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4127">
+      <c r="A4127" s="2" t="n">
+        <v>46046</v>
+      </c>
+      <c r="B4127" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4128">
+      <c r="A4128" s="2" t="n">
+        <v>46047</v>
+      </c>
+      <c r="B4128" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4129">
+      <c r="A4129" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B4129" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4130">
+      <c r="A4130" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B4130" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4131">
+      <c r="A4131" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B4131" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4132">
+      <c r="A4132" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B4132" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4132"/>
+  <dimension ref="A1:B4137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33492,6 +33492,46 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4133">
+      <c r="A4133" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B4133" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4134">
+      <c r="A4134" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B4134" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4135">
+      <c r="A4135" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B4135" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4136">
+      <c r="A4136" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B4136" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4137">
+      <c r="A4137" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B4137" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4137"/>
+  <dimension ref="A1:B4138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33532,6 +33532,14 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4138">
+      <c r="A4138" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B4138" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4138"/>
+  <dimension ref="A1:B4144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33540,6 +33540,54 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4139">
+      <c r="A4139" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B4139" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4140">
+      <c r="A4140" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B4140" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4141">
+      <c r="A4141" s="2" t="n">
+        <v>46060</v>
+      </c>
+      <c r="B4141" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4142">
+      <c r="A4142" s="2" t="n">
+        <v>46061</v>
+      </c>
+      <c r="B4142" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4143">
+      <c r="A4143" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B4143" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4144">
+      <c r="A4144" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B4144" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4144"/>
+  <dimension ref="A1:B4145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33588,6 +33588,14 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4145">
+      <c r="A4145" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B4145" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4145"/>
+  <dimension ref="A1:B4146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33596,6 +33596,14 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4146">
+      <c r="A4146" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B4146" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4146"/>
+  <dimension ref="A1:B4147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33604,6 +33604,14 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4147">
+      <c r="A4147" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B4147" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4147"/>
+  <dimension ref="A1:B4151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33612,6 +33612,38 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4148">
+      <c r="A4148" s="2" t="n">
+        <v>46067</v>
+      </c>
+      <c r="B4148" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4149">
+      <c r="A4149" s="2" t="n">
+        <v>46068</v>
+      </c>
+      <c r="B4149" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4150">
+      <c r="A4150" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B4150" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4151">
+      <c r="A4151" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B4151" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4151"/>
+  <dimension ref="A1:B4152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33644,6 +33644,14 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4152">
+      <c r="A4152" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B4152" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4157"/>
+  <dimension ref="A1:B4164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33680,6 +33680,62 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4158">
+      <c r="A4158" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B4158" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4159">
+      <c r="A4159" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B4159" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4160">
+      <c r="A4160" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B4160" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4161">
+      <c r="A4161" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B4161" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4162">
+      <c r="A4162" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B4162" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4163">
+      <c r="A4163" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B4163" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4164">
+      <c r="A4164" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B4164" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4164"/>
+  <dimension ref="A1:B4171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33736,6 +33736,62 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4165">
+      <c r="A4165" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B4165" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4166">
+      <c r="A4166" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B4166" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4167">
+      <c r="A4167" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B4167" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4168">
+      <c r="A4168" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B4168" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4169">
+      <c r="A4169" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="B4169" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4170">
+      <c r="A4170" s="1" t="n">
+        <v>46089</v>
+      </c>
+      <c r="B4170" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4171">
+      <c r="A4171" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B4171" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4171"/>
+  <dimension ref="A1:B4178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33792,6 +33792,62 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4172">
+      <c r="A4172" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B4172" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4173">
+      <c r="A4173" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B4173" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4174">
+      <c r="A4174" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B4174" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4175">
+      <c r="A4175" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B4175" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4176">
+      <c r="A4176" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B4176" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4177">
+      <c r="A4177" s="1" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B4177" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4178">
+      <c r="A4178" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B4178" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4178"/>
+  <dimension ref="A1:B4185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33848,6 +33848,62 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4179">
+      <c r="A4179" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B4179" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4180">
+      <c r="A4180" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B4180" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4181">
+      <c r="A4181" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B4181" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4182">
+      <c r="A4182" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B4182" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4183">
+      <c r="A4183" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B4183" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4184">
+      <c r="A4184" s="1" t="n">
+        <v>46103</v>
+      </c>
+      <c r="B4184" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4185">
+      <c r="A4185" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B4185" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4185"/>
+  <dimension ref="A1:B4192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33904,6 +33904,62 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4186">
+      <c r="A4186" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B4186" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4187">
+      <c r="A4187" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B4187" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4188">
+      <c r="A4188" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B4188" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4189">
+      <c r="A4189" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B4189" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4190">
+      <c r="A4190" s="1" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B4190" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4191">
+      <c r="A4191" s="1" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B4191" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4192">
+      <c r="A4192" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B4192" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4192"/>
+  <dimension ref="A1:B4199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33960,6 +33960,62 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4193">
+      <c r="A4193" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B4193" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4194">
+      <c r="A4194" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B4194" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4195">
+      <c r="A4195" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B4195" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4196">
+      <c r="A4196" s="1" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B4196" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4197">
+      <c r="A4197" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B4197" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4198">
+      <c r="A4198" s="1" t="n">
+        <v>46117</v>
+      </c>
+      <c r="B4198" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4199">
+      <c r="A4199" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B4199" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4199"/>
+  <dimension ref="A1:B4206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34016,6 +34016,62 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4200">
+      <c r="A4200" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B4200" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4201">
+      <c r="A4201" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B4201" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4202">
+      <c r="A4202" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B4202" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4203">
+      <c r="A4203" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B4203" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4204">
+      <c r="A4204" s="1" t="n">
+        <v>46123</v>
+      </c>
+      <c r="B4204" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4205">
+      <c r="A4205" s="1" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B4205" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4206">
+      <c r="A4206" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B4206" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4206"/>
+  <dimension ref="A1:B4213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34072,6 +34072,62 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4207">
+      <c r="A4207" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B4207" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4208">
+      <c r="A4208" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B4208" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4209">
+      <c r="A4209" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B4209" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4210">
+      <c r="A4210" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B4210" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4211">
+      <c r="A4211" s="1" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B4211" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4212">
+      <c r="A4212" s="1" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B4212" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4213">
+      <c r="A4213" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B4213" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4213"/>
+  <dimension ref="A1:B4220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34128,6 +34128,62 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4214">
+      <c r="A4214" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B4214" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4215">
+      <c r="A4215" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B4215" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4216">
+      <c r="A4216" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B4216" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4217">
+      <c r="A4217" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B4217" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4218">
+      <c r="A4218" s="1" t="n">
+        <v>46137</v>
+      </c>
+      <c r="B4218" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4219">
+      <c r="A4219" s="1" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B4219" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4220">
+      <c r="A4220" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B4220" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4220"/>
+  <dimension ref="A1:B4227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34184,6 +34184,62 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4221">
+      <c r="A4221" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B4221" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4222">
+      <c r="A4222" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B4222" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4223">
+      <c r="A4223" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B4223" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4224">
+      <c r="A4224" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B4224" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4225">
+      <c r="A4225" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B4225" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4226">
+      <c r="A4226" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B4226" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4227">
+      <c r="A4227" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B4227" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4227"/>
+  <dimension ref="A1:B4255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34240,6 +34240,230 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4228">
+      <c r="A4228" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B4228" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4229">
+      <c r="A4229" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B4229" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4230">
+      <c r="A4230" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B4230" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4231">
+      <c r="A4231" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B4231" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4232">
+      <c r="A4232" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B4232" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4233">
+      <c r="A4233" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B4233" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4234">
+      <c r="A4234" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B4234" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4235">
+      <c r="A4235" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B4235" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4236">
+      <c r="A4236" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B4236" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4237">
+      <c r="A4237" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B4237" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4238">
+      <c r="A4238" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B4238" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4239">
+      <c r="A4239" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B4239" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4240">
+      <c r="A4240" s="1" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B4240" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4241">
+      <c r="A4241" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B4241" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4242">
+      <c r="A4242" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B4242" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4243">
+      <c r="A4243" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B4243" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4244">
+      <c r="A4244" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B4244" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4245">
+      <c r="A4245" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B4245" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4246">
+      <c r="A4246" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B4246" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4247">
+      <c r="A4247" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B4247" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4248">
+      <c r="A4248" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B4248" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4249">
+      <c r="A4249" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B4249" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4250">
+      <c r="A4250" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B4250" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4251">
+      <c r="A4251" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B4251" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4252">
+      <c r="A4252" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B4252" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4253">
+      <c r="A4253" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B4253" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4254">
+      <c r="A4254" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B4254" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4255">
+      <c r="A4255" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B4255" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4255"/>
+  <dimension ref="A1:B4285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34464,6 +34464,246 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4256">
+      <c r="A4256" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B4256" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4257">
+      <c r="A4257" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B4257" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4258">
+      <c r="A4258" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B4258" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4259">
+      <c r="A4259" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B4259" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4260">
+      <c r="A4260" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B4260" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4261">
+      <c r="A4261" s="1" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B4261" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4262">
+      <c r="A4262" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B4262" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4263">
+      <c r="A4263" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B4263" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4264">
+      <c r="A4264" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B4264" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4265">
+      <c r="A4265" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B4265" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4266">
+      <c r="A4266" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B4266" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4267">
+      <c r="A4267" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B4267" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4268">
+      <c r="A4268" s="1" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B4268" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4269">
+      <c r="A4269" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B4269" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4270">
+      <c r="A4270" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B4270" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4271">
+      <c r="A4271" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B4271" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4272">
+      <c r="A4272" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B4272" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4273">
+      <c r="A4273" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B4273" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4274">
+      <c r="A4274" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B4274" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4275">
+      <c r="A4275" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B4275" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4276">
+      <c r="A4276" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B4276" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4277">
+      <c r="A4277" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B4277" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4278">
+      <c r="A4278" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B4278" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4279">
+      <c r="A4279" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B4279" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4280">
+      <c r="A4280" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B4280" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4281">
+      <c r="A4281" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B4281" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4282">
+      <c r="A4282" s="1" t="n">
+        <v>46201</v>
+      </c>
+      <c r="B4282" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4283">
+      <c r="A4283" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B4283" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4284">
+      <c r="A4284" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B4284" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4285">
+      <c r="A4285" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B4285" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4285"/>
+  <dimension ref="A1:B4316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34704,6 +34704,254 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4286">
+      <c r="A4286" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B4286" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4287">
+      <c r="A4287" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B4287" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4288">
+      <c r="A4288" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B4288" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4289">
+      <c r="A4289" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B4289" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4290">
+      <c r="A4290" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B4290" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4291">
+      <c r="A4291" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B4291" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4292">
+      <c r="A4292" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B4292" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4293">
+      <c r="A4293" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B4293" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4294">
+      <c r="A4294" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B4294" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4295">
+      <c r="A4295" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B4295" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4296">
+      <c r="A4296" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B4296" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4297">
+      <c r="A4297" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B4297" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4298">
+      <c r="A4298" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B4298" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4299">
+      <c r="A4299" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B4299" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4300">
+      <c r="A4300" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B4300" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4301">
+      <c r="A4301" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B4301" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4302">
+      <c r="A4302" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B4302" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4303">
+      <c r="A4303" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B4303" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4304">
+      <c r="A4304" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B4304" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4305">
+      <c r="A4305" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B4305" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4306">
+      <c r="A4306" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B4306" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4307">
+      <c r="A4307" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B4307" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4308">
+      <c r="A4308" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B4308" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4309">
+      <c r="A4309" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B4309" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4310">
+      <c r="A4310" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B4310" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4311">
+      <c r="A4311" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B4311" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4312">
+      <c r="A4312" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B4312" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4313">
+      <c r="A4313" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B4313" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4314">
+      <c r="A4314" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B4314" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4315">
+      <c r="A4315" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B4315" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4316">
+      <c r="A4316" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B4316" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/downloads/ccyb_diffusion.xlsx
+++ b/reports/downloads/ccyb_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4316"/>
+  <dimension ref="A1:B4333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34952,6 +34952,142 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4317">
+      <c r="A4317" s="1" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B4317" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4318">
+      <c r="A4318" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B4318" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4319">
+      <c r="A4319" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B4319" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4320">
+      <c r="A4320" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B4320" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4321">
+      <c r="A4321" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B4321" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4322">
+      <c r="A4322" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B4322" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4323">
+      <c r="A4323" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B4323" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4324">
+      <c r="A4324" s="1" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B4324" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4325">
+      <c r="A4325" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B4325" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4326">
+      <c r="A4326" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B4326" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4327">
+      <c r="A4327" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B4327" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4328">
+      <c r="A4328" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B4328" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4329">
+      <c r="A4329" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B4329" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4330">
+      <c r="A4330" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B4330" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4331">
+      <c r="A4331" s="1" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B4331" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4332">
+      <c r="A4332" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B4332" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4333">
+      <c r="A4333" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B4333" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
